--- a/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aline est dans le salon. Papa plie une couverture. Aline est devant l'écran. Les couleurs bougent. Maman s'assoit près d'elle. Maman dit : fini. L'adulte dit fini. Aline écoute. Elle va éteindre. Aline éteint l'écran. L'écran devient noir. Elle pose la télécommande. Maman dit : on prend un autre jeu. Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.</t>
+          <t>Aline est dans le salon. Papa plie une couverture. Aline est devant l'écran. Les couleurs bougent. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Aline écoute. Elle va éteindre. Aline éteint l'écran. L'écran devient noir. Elle pose la télécommande. On prend un autre jeu. Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aline est dans le salon. Papa plie une couverture. Aline est devant l'écran. Les couleurs bougent. Maman s'assoit près d'elle.
+maman|Fini. L'adulte dit fini.
+narrateur|Aline écoute. Elle va éteindre. Aline éteint l'écran. L'écran devient noir. Elle pose la télécommande.
+maman|On prend un autre jeu.
+narrateur|Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Aline ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maman a dit fini. Aline a éteint. Elle a pris un autre jeu. La dinette, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les tasses sont rangées. Aline dit merci à maman. Le salon est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Maman dit fini. Que fait Aline ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Maman a dit fini. Aline a éteint. Elle a pris un autre jeu. La dinette, c'était bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Les tasses sont rangées. Aline dit merci à maman. Le salon est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aline éteint et joue à la dinette</t>
+          <t>La dinette en bois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une couverture tiède sent la laine. Maman dit fini. Victorina éteint. Elle pose une tasse. Ça sent le bois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aline est dans le salon. Papa plie une couverture. Aline est devant l'écran. Les couleurs bougent. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Aline écoute. Elle va éteindre. Aline éteint l'écran. L'écran devient noir. Elle pose la télécommande. On prend un autre jeu. Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.</t>
+          <t>Une couverture encore tiède attend. Elle sent la laine. Papa la plie, tout doucement. La pluie tape sur le toit. Toc, toc, toc. Le tapis est doux. Une tasse en bois brille un peu. Elle est près du canapé. La couverture est chaude. Victorina, viens. Tu entends la pluie ? Oui, maman. Toc toc. Oui. Sur le toit. En ce moment, l'écran brille. Les couleurs bougent. Victorina est devant l'écran. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Victorina écoute. C'est fini. On va éteindre. Victorina va éteindre. Victorina éteint l'écran. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Victorina choisit la dinette. La dinette est en bois. Ça sent le bois. Elle pose une tasse. La tasse est petite et ronde. Papa pose une cuillère. La tasse. Oui. Une petite tasse. Et la cuillère ? La cuillère. Victorina verse de l'eau factice. Ça ne mouille pas. Merci. C'est du bon travail. On goûte ? C'est du thé. Du thé tiède. L'écran est éteint. Oui. Un autre jeu, c'est bien. Elles rangent les tasses. Le bois fait un petit clic. On range la cuillère aussi ? Oui, papa. La cuillère rentre dans la boîte. Bravo. La pluie continue, dehors.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aline est dans le salon. Papa plie une couverture. Aline est devant l'écran. Les couleurs bougent. Maman s'assoit près d'elle.
-maman|Fini. L'adulte dit fini.
-narrateur|Aline écoute. Elle va éteindre. Aline éteint l'écran. L'écran devient noir. Elle pose la télécommande.
+          <t>narrateur|Une couverture encore tiède attend.
+narrateur|Elle sent la laine.
+narrateur|Papa la plie, tout doucement.
+narrateur|La pluie tape sur le toit.
+narrateur|Toc, toc, toc.
+narrateur|Le tapis est doux.
+narrateur|Une tasse en bois brille un peu.
+narrateur|Elle est près du canapé.
+papa|La couverture est chaude.
+maman|Victorina, viens.
+maman|Tu entends la pluie ?
+enfant-f|Oui, maman.
+enfant-f|Toc toc.
+papa|Oui.
+papa|Sur le toit.
+narrateur|En ce moment, l'écran brille.
+narrateur|Les couleurs bougent.
+narrateur|Victorina est devant l'écran.
+narrateur|Maman s'assoit près d'elle.
+maman|Fini.
+narrateur|L'adulte dit fini.
+narrateur|Victorina écoute.
+enfant-f|C'est fini.
+maman|On va éteindre.
+narrateur|Victorina va éteindre.
+narrateur|Victorina éteint l'écran.
+narrateur|L'écran devient noir.
+narrateur|Elle pose la télécommande.
+maman|Bravo, Victorina.
+maman|Tu as éteint.
 maman|On prend un autre jeu.
-narrateur|Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Un autre jeu.
+papa|Tu choisis ?
+narrateur|Victorina choisit la dinette.
+narrateur|La dinette est en bois.
+narrateur|Ça sent le bois.
+narrateur|Elle pose une tasse.
+narrateur|La tasse est petite et ronde.
+narrateur|Papa pose une cuillère.
+enfant-f|La tasse.
+papa|Oui.
+papa|Une petite tasse.
+maman|Et la cuillère ?
+enfant-f|La cuillère.
+narrateur|Victorina verse de l'eau factice.
+narrateur|Ça ne mouille pas.
+maman|Merci.
+maman|C'est du bon travail.
+papa|On goûte ?
+enfant-f|C'est du thé.
+papa|Du thé tiède.
+enfant-f|L'écran est éteint.
+maman|Oui.
+maman|Un autre jeu, c'est bien.
+narrateur|Elles rangent les tasses.
+narrateur|Le bois fait un petit clic.
+papa|On range la cuillère aussi ?
+enfant-f|Oui, papa.
+narrateur|La cuillère rentre dans la boîte.
+papa|Bravo.
+narrateur|La pluie continue, dehors.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie_toit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maman dit fini. Que fait Aline ?</t>
+          <t>Maman dit fini. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maman dit fini. Que fait Aline ?</t>
+          <t>narrateur|Maman dit fini.
+narrateur|Que fait Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maman a dit fini. Aline a éteint. Elle a pris un autre jeu. La dinette, c'était bien.</t>
+          <t>Maman a dit fini. L'adulte a dit fini. Victorina a éteint. Elle a pris un autre jeu. Tu as éteint ? Oui, maman. Et après ? Un autre jeu. Bravo. La dinette, c'était bien. Victorina touche la tasse. Le bois est lisse. Tu verses encore un peu ? Oui, papa. La cuillère reste dans la tasse. Ça sent encore le bois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1745,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maman a dit fini. Aline a éteint. Elle a pris un autre jeu. La dinette, c'était bien.</t>
+          <t>narrateur|Maman a dit fini.
+narrateur|L'adulte a dit fini.
+narrateur|Victorina a éteint.
+narrateur|Elle a pris un autre jeu.
+maman|Tu as éteint ?
+enfant-f|Oui, maman.
+papa|Et après ?
+enfant-f|Un autre jeu.
+maman|Bravo.
+maman|La dinette, c'était bien.
+narrateur|Victorina touche la tasse.
+narrateur|Le bois est lisse.
+papa|Tu verses encore un peu ?
+enfant-f|Oui, papa.
+narrateur|La cuillère reste dans la tasse.
+narrateur|Ça sent encore le bois.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Les tasses sont rangées. Aline dit merci à maman. Le salon est calme.</t>
+          <t>Les tasses sont rangées. On range la télécommande ? Victorina pose la télécommande. Tu as fini de ranger ? Oui, papa. Bravo. Merci, maman. Merci, Victorina. On plie encore la couverture ? Papa plie le dernier coin. Le salon est calme. La couverture reste pliée. La laine sent encore le chaud. Elle est douce. Oui. Tout doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1924,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Les tasses sont rangées. Aline dit merci à maman. Le salon est calme.</t>
+          <t>narrateur|Les tasses sont rangées.
+maman|On range la télécommande ?
+narrateur|Victorina pose la télécommande.
+papa|Tu as fini de ranger ?
+enfant-f|Oui, papa.
+papa|Bravo.
+enfant-f|Merci, maman.
+maman|Merci, Victorina.
+papa|On plie encore la couverture ?
+narrateur|Papa plie le dernier coin.
+narrateur|Le salon est calme.
+narrateur|La couverture reste pliée.
+narrateur|La laine sent encore le chaud.
+enfant-f|Elle est douce.
+papa|Oui.
+papa|Tout doux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La petite tasse attend. L'écran est éteint. Oui. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2107,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La petite tasse attend.
+enfant-f|L'écran est éteint.
+papa|Oui.
+maman|Bravo, Victorina.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une couverture encore tiède attend. Elle sent la laine. Papa la plie, tout doucement. La pluie tape sur le toit. Toc, toc, toc. Le tapis est doux. Une tasse en bois brille un peu. Elle est près du canapé. La couverture est chaude. Victorina, viens. Tu entends la pluie ? Oui, maman. Toc toc. Oui. Sur le toit. En ce moment, l'écran brille. Les couleurs bougent. Victorina est devant l'écran. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Victorina écoute. C'est fini. On va éteindre. Victorina va éteindre. Victorina éteint l'écran. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Victorina choisit la dinette. La dinette est en bois. Ça sent le bois. Elle pose une tasse. La tasse est petite et ronde. Papa pose une cuillère. La tasse. Oui. Une petite tasse. Et la cuillère ? La cuillère. Victorina verse de l'eau factice. Ça ne mouille pas. Merci. C'est du bon travail. On goûte ? C'est du thé. Du thé tiède. L'écran est éteint. Oui. Un autre jeu, c'est bien. Elles rangent les tasses. Le bois fait un petit clic. On range la cuillère aussi ? Oui, papa. La cuillère rentre dans la boîte. Bravo. La pluie continue, dehors.</t>
+          <t>Une couverture encore tiède attend. Elle sent la laine. Papa la plie, tout doucement. La pluie tape sur le toit. Toc, toc, toc. Le tapis est doux. Une tasse en bois brille un peu. Elle est près du canapé. La couverture est chaude. Victorina, viens. Tu entends la pluie ? Oui, maman. Toc toc. Oui. Sur le toit. En ce moment, l'écran brille. Les couleurs bougent. Victorina est devant l'écran. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Victorina écoute. C'est fini. On va éteindre. Victorina va éteindre. Victorina éteint l'écran. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Victorina choisit la dinette. La dinette est en bois. Ça sent le bois. Elle pose une tasse. La tasse est petite et ronde. Papa pose une cuillère. La tasse. Oui. Une petite tasse. Et la cuillère ? La cuillère. Victorina verse de l'eau factice. Ça ne mouille pas. Merci. On goûte ? C'est du thé. Du thé tiède. L'écran est éteint. Oui. Un autre jeu, c'est bien. Elles rangent les tasses. Le bois fait un petit clic. On range la cuillère aussi ? Oui, papa. La cuillère rentre dans la boîte. Bravo. La pluie continue, dehors.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Aline est dans le salon. Papa plie une couverture. Aline est devant l'écran. Les couleurs bougent. Maman s'assoit près d'elle. Maman dit : fini. L'adulte dit fini. Aline écoute. Elle va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Aline éteint l'écran. L'écran devient noir. Elle pose la télécommande. Maman dit : on prend un autre jeu. Aline choisit la dinette en bois. Elle pose une tasse. Papa pose une cuillère. Ça sent le bois. Aline verse de l'eau factice. Maman dit merci. Aline sourit. L'écran est éteint. Un autre jeu, c'est bien. Elles rangent les tasses. Aline a éteint. Elle a choisi un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une couverture encore tiède attend. Elle sent la laine. Papa la plie, tout doucement. La pluie tape sur le toit. Toc, toc, toc. Le tapis est doux. Une tasse en bois brille un peu. Elle est près du canapé. La couverture est chaude. Victorina, viens. Tu entends la pluie ? Oui, maman. Toc toc. Oui. Sur le toit. En ce moment, l'écran brille. Les couleurs bougent. Victorina est devant l'écran. Maman s'assoit près d'elle. Fini. L'adulte dit fini. Victorina écoute. C'est fini. On va éteindre. Victorina va éteindre. Victorina éteint l'écran. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Victorina choisit la dinette. La dinette est en bois. Ça sent le bois. Elle pose une tasse. La tasse est petite et ronde. Papa pose une cuillère. La tasse. Oui. Une petite tasse. Et la cuillère ? La cuillère. Victorina verse de l'eau factice. Ça ne mouille pas. Merci. On goûte ? C'est du thé. Du thé tiède. L'écran est éteint. Oui. Un autre jeu, c'est bien. Elles rangent les tasses. Le bois fait un petit clic. On range la cuillère aussi ? Oui, papa. La cuillère rentre dans la boîte. Bravo. La pluie continue, dehors.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1371,7 +1371,6 @@
 narrateur|Victorina verse de l'eau factice.
 narrateur|Ça ne mouille pas.
 maman|Merci.
-maman|C'est du bon travail.
 papa|On goûte ?
 enfant-f|C'est du thé.
 papa|Du thé tiède.
@@ -1421,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman dit fini. Que fait Aline ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman dit fini. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1575,6 @@
 narrateur|Que fait Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,7 +1604,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman a dit fini. Aline a éteint. Elle a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. La dinette, c'était bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman a dit fini. L'adulte a dit fini. Victorina a éteint. Elle a pris un autre jeu. Tu as éteint ? Oui, maman. Et après ? Un autre jeu. Bravo. La dinette, c'était bien. Victorina touche la tasse. Le bois est lisse. Tu verses encore un peu ? Oui, papa. La cuillère reste dans la tasse. Ça sent encore le bois.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1763,7 +1761,6 @@
 narrateur|Ça sent encore le bois.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les tasses sont rangées. Aline dit merci à maman. Le salon est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les tasses sont rangées. On range la télécommande ? Victorina pose la télécommande. Tu as fini de ranger ? Oui, papa. Bravo. Merci, maman. Merci, Victorina. On plie encore la couverture ? Papa plie le dernier coin. Le salon est calme. La couverture reste pliée. La laine sent encore le chaud. Elle est douce. Oui. Tout doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,7 +1939,6 @@
 papa|Tout doux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La petite tasse attend. L'écran est éteint. Oui. Bravo, Victorina. L'histoire est finie.</t>
+          <t>La petite tasse attend. L'écran est éteint. Oui. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La petite tasse attend. L'écran est éteint. Oui. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2110,11 +2106,9 @@
           <t>narrateur|La petite tasse attend.
 enfant-f|L'écran est éteint.
 papa|Oui.
-maman|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Victorina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, couverture, dinette en bois</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aline, maman, papa</t>
+          <t>Victorina, maman, papa</t>
         </is>
       </c>
     </row>
